--- a/docs/deliverables/07_セキュリティ/セキュリティ監査報告書.xlsx
+++ b/docs/deliverables/07_セキュリティ/セキュリティ監査報告書.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文書管理" sheetId="1" r:id="R9c3c5680792d4769"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="監査情報" sheetId="2" r:id="R0e25a874d7d942f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="確認結果" sheetId="3" r:id="R862fdb61120c4a48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEC-FIX-001_Outlookトークンのログ露出" sheetId="4" r:id="R870f4fcf48e64855"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEC-FIX-002_未使用トークンの増加" sheetId="5" r:id="R6e4bc5a5e5804741"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEC-FIX-003_コンテナ間到達範囲" sheetId="6" r:id="R63a25331db4d4120"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEC-FIX-004_コンテナ権限" sheetId="7" r:id="Ra1aba4cb3c494fd1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本番前に必須の対策" sheetId="8" r:id="Rfcc89afd4a364582"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="残存リスク" sheetId="9" r:id="R66d2f7068d774c99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文書管理" sheetId="1" r:id="R95508ef0ceb148d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="監査情報" sheetId="2" r:id="Rf52e64928cf94145"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="確認結果" sheetId="3" r:id="R609463550bd34bfc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEC-FIX-001_Outlookトークンのログ露出" sheetId="4" r:id="R693f190e8bc84042"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEC-FIX-002_未使用トークンの増加" sheetId="5" r:id="R4ca0ed08c11649a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEC-FIX-003_コンテナ間到達範囲" sheetId="6" r:id="Rc6d3517b5398434b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEC-FIX-004_コンテナ権限" sheetId="7" r:id="R5af7b88efe744cee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本番前に必須の対策" sheetId="8" r:id="Rd83278e1c57e4a15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="残存リスク" sheetId="9" r:id="Rcb000082964c4a42"/>
   </x:sheets>
 </x:workbook>
 </file>
